--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328603</v>
+        <v>124326926</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,43 +917,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596290</v>
+        <v>596167</v>
       </c>
       <c r="R4" t="n">
-        <v>6924176</v>
+        <v>6924177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,19 +978,9 @@
           <t>2025-04-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,22 +995,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124326926</v>
+        <v>124329435</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,34 +1023,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Spår 3 tecken hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596167</v>
+        <v>596198</v>
       </c>
       <c r="R5" t="n">
-        <v>6924177</v>
+        <v>6924172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,9 +1088,19 @@
           <t>2025-04-22</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,22 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124329435</v>
+        <v>124328662</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,46 +1139,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spår 3 tecken hackspett , Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596198</v>
+        <v>596290</v>
       </c>
       <c r="R6" t="n">
-        <v>6924172</v>
+        <v>6924176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124326926</v>
+        <v>124328828</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,38 +917,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596167</v>
+        <v>596290</v>
       </c>
       <c r="R4" t="n">
-        <v>6924177</v>
+        <v>6924176</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,9 +983,19 @@
           <t>2025-04-22</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,12 +1010,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1127,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124328662</v>
+        <v>124326926</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,43 +1154,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596290</v>
+        <v>596167</v>
       </c>
       <c r="R6" t="n">
-        <v>6924176</v>
+        <v>6924177</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,19 +1215,9 @@
           <t>2025-04-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328828</v>
+        <v>124326926</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,43 +917,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596290</v>
+        <v>596167</v>
       </c>
       <c r="R4" t="n">
-        <v>6924176</v>
+        <v>6924177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,19 +978,9 @@
           <t>2025-04-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,22 +995,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124329435</v>
+        <v>124328828</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,46 +1019,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spår 3 tecken hackspett , Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596198</v>
+        <v>596290</v>
       </c>
       <c r="R5" t="n">
-        <v>6924172</v>
+        <v>6924176</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124326926</v>
+        <v>124329435</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,34 +1140,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Spår 3 tecken hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596167</v>
+        <v>596198</v>
       </c>
       <c r="R6" t="n">
-        <v>6924177</v>
+        <v>6924172</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,9 +1205,19 @@
           <t>2025-04-22</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1356,6 +1356,1988 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124929330</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96979</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>596232</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6924082</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124927331</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>596228</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6924195</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124928083</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596173</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6924184</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124929444</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>596259</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6924079</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124929949</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>596267</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6924058</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124925426</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96979</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>596395</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6924217</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124931729</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>596350</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6924076</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124927907</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>596183</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6924165</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124930808</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>596344</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6924086</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124931273</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>596323</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6924104</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124926296</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>596339</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6924185</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124926902</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>596234</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6924156</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124925523</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>596346</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6924199</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124927193</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>596249</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6924197</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124927157</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tjäder bas, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>596290</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6924176</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124931177</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>596344</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6924086</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124928235</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>596183</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6924165</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1587,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124928083</v>
+        <v>124925426</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,39 +1603,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596173</v>
+        <v>596395</v>
       </c>
       <c r="R10" t="n">
-        <v>6924184</v>
+        <v>6924217</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1672,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1816,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124929949</v>
+        <v>124928083</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,38 +1823,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596267</v>
+        <v>596173</v>
       </c>
       <c r="R12" t="n">
-        <v>6924058</v>
+        <v>6924184</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,10 +1928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124925426</v>
+        <v>124929949</v>
       </c>
       <c r="B13" t="n">
-        <v>96979</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,25 +1940,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596395</v>
+        <v>596267</v>
       </c>
       <c r="R13" t="n">
-        <v>6924217</v>
+        <v>6924058</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124326926</v>
+        <v>124328662</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,38 +917,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596167</v>
+        <v>596290</v>
       </c>
       <c r="R4" t="n">
-        <v>6924177</v>
+        <v>6924176</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,9 +983,19 @@
           <t>2025-04-22</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,22 +1010,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124328828</v>
+        <v>124329435</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,43 +1034,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Spår 3 tecken hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596290</v>
+        <v>596198</v>
       </c>
       <c r="R5" t="n">
-        <v>6924176</v>
+        <v>6924172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124329435</v>
+        <v>124326926</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,42 +1158,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spår 3 tecken hackspett , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596198</v>
+        <v>596167</v>
       </c>
       <c r="R6" t="n">
-        <v>6924172</v>
+        <v>6924177</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,19 +1215,9 @@
           <t>2025-04-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124929330</v>
+        <v>124925426</v>
       </c>
       <c r="B8" t="n">
         <v>96979</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596232</v>
+        <v>596395</v>
       </c>
       <c r="R8" t="n">
-        <v>6924082</v>
+        <v>6924217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124927331</v>
+        <v>124931177</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,31 +1482,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596228</v>
+        <v>596344</v>
       </c>
       <c r="R9" t="n">
-        <v>6924195</v>
+        <v>6924086</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1560,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,22 +1580,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124925426</v>
+        <v>124926902</v>
       </c>
       <c r="B10" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,38 +1604,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596395</v>
+        <v>596234</v>
       </c>
       <c r="R10" t="n">
-        <v>6924217</v>
+        <v>6924156</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,7 +1682,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,22 +1702,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124929444</v>
+        <v>124927157</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,34 +1730,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596259</v>
+        <v>596290</v>
       </c>
       <c r="R11" t="n">
-        <v>6924079</v>
+        <v>6924176</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1774,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,7 +1804,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,19 +1824,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124928083</v>
+        <v>124928235</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1847,7 +1872,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1856,10 +1881,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596173</v>
+        <v>596183</v>
       </c>
       <c r="R12" t="n">
-        <v>6924184</v>
+        <v>6924165</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,7 +1916,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1901,7 +1926,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,12 +1941,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2040,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124931729</v>
+        <v>124929444</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,43 +2081,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596350</v>
+        <v>596259</v>
       </c>
       <c r="R14" t="n">
-        <v>6924076</v>
+        <v>6924079</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2140,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2150,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,22 +2165,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124927907</v>
+        <v>124928083</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,30 +2189,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2205,10 +2222,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596183</v>
+        <v>596173</v>
       </c>
       <c r="R15" t="n">
-        <v>6924165</v>
+        <v>6924184</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,19 +2282,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124930808</v>
+        <v>124927331</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2322,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596344</v>
+        <v>596228</v>
       </c>
       <c r="R16" t="n">
-        <v>6924086</v>
+        <v>6924195</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,12 +2399,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2506,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124926296</v>
+        <v>124927193</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2522,16 +2539,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2547,14 +2564,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596339</v>
+        <v>596249</v>
       </c>
       <c r="R18" t="n">
-        <v>6924185</v>
+        <v>6924197</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2613,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,22 +2633,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124926902</v>
+        <v>124931729</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,27 +2661,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2668,10 +2694,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596234</v>
+        <v>596350</v>
       </c>
       <c r="R19" t="n">
-        <v>6924156</v>
+        <v>6924076</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2703,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,12 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2766,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124925523</v>
+        <v>124930808</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2757,38 +2778,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596346</v>
+        <v>596344</v>
       </c>
       <c r="R20" t="n">
-        <v>6924199</v>
+        <v>6924086</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2820,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2830,7 +2856,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,22 +2871,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124927193</v>
+        <v>124929330</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2869,43 +2895,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596249</v>
+        <v>596232</v>
       </c>
       <c r="R21" t="n">
-        <v>6924197</v>
+        <v>6924082</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2958,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,12 +2968,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2967,22 +2983,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124927157</v>
+        <v>124927907</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,43 +3007,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596290</v>
+        <v>596183</v>
       </c>
       <c r="R22" t="n">
-        <v>6924176</v>
+        <v>6924165</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +3074,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,12 +3084,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3101,10 +3111,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124931177</v>
+        <v>124925523</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3117,39 +3127,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596344</v>
+        <v>596346</v>
       </c>
       <c r="R23" t="n">
-        <v>6924086</v>
+        <v>6924199</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3181,7 +3186,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3191,12 +3196,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,22 +3211,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124928235</v>
+        <v>124926296</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3235,31 +3235,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596183</v>
+        <v>596339</v>
       </c>
       <c r="R24" t="n">
-        <v>6924165</v>
+        <v>6924185</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3328,12 +3328,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328662</v>
+        <v>124328828</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124329435</v>
+        <v>124326926</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,42 +1038,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spår 3 tecken hackspett , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596198</v>
+        <v>596167</v>
       </c>
       <c r="R5" t="n">
-        <v>6924172</v>
+        <v>6924177</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,19 +1095,9 @@
           <t>2025-04-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1112,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124326926</v>
+        <v>124329435</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,34 +1140,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Spår 3 tecken hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596167</v>
+        <v>596198</v>
       </c>
       <c r="R6" t="n">
-        <v>6924177</v>
+        <v>6924172</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,9 +1205,19 @@
           <t>2025-04-22</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124925426</v>
+        <v>124930808</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,34 +1374,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596395</v>
+        <v>596344</v>
       </c>
       <c r="R8" t="n">
-        <v>6924217</v>
+        <v>6924086</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124931177</v>
+        <v>124925426</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,43 +1487,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596344</v>
+        <v>596395</v>
       </c>
       <c r="R9" t="n">
-        <v>6924086</v>
+        <v>6924217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,12 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124926902</v>
+        <v>124928083</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,43 +1599,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596234</v>
+        <v>596173</v>
       </c>
       <c r="R10" t="n">
-        <v>6924156</v>
+        <v>6924184</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,12 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,12 +1692,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1836,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124928235</v>
+        <v>124925523</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,43 +1838,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596183</v>
+        <v>596346</v>
       </c>
       <c r="R12" t="n">
-        <v>6924165</v>
+        <v>6924199</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1926,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,22 +1926,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124929949</v>
+        <v>124927193</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,34 +1954,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596267</v>
+        <v>596249</v>
       </c>
       <c r="R13" t="n">
-        <v>6924058</v>
+        <v>6924197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2038,7 +2028,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,22 +2048,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124929444</v>
+        <v>124929330</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>96979</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,25 +2072,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,10 +2100,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596259</v>
+        <v>596232</v>
       </c>
       <c r="R14" t="n">
-        <v>6924079</v>
+        <v>6924082</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2150,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124928083</v>
+        <v>124929444</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2189,43 +2184,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596173</v>
+        <v>596259</v>
       </c>
       <c r="R15" t="n">
-        <v>6924184</v>
+        <v>6924079</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2257,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124927331</v>
+        <v>124926902</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,43 +2296,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596228</v>
+        <v>596234</v>
       </c>
       <c r="R16" t="n">
-        <v>6924195</v>
+        <v>6924156</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,7 +2364,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,7 +2374,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,22 +2394,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124931273</v>
+        <v>124927907</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,38 +2418,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596323</v>
+        <v>596183</v>
       </c>
       <c r="R17" t="n">
-        <v>6924104</v>
+        <v>6924165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2486,7 +2485,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2495,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,22 +2510,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124927193</v>
+        <v>124931729</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,27 +2538,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2568,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596249</v>
+        <v>596350</v>
       </c>
       <c r="R18" t="n">
-        <v>6924197</v>
+        <v>6924076</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2603,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,12 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,22 +2631,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124931729</v>
+        <v>124931177</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2661,43 +2659,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596350</v>
+        <v>596344</v>
       </c>
       <c r="R19" t="n">
-        <v>6924076</v>
+        <v>6924086</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2733,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,22 +2753,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124930808</v>
+        <v>124926296</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2778,31 +2777,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2811,10 +2810,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596344</v>
+        <v>596339</v>
       </c>
       <c r="R20" t="n">
-        <v>6924086</v>
+        <v>6924185</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2846,7 +2845,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2856,7 +2855,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,10 +2882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124929330</v>
+        <v>124931273</v>
       </c>
       <c r="B21" t="n">
-        <v>96979</v>
+        <v>90977</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2899,21 +2898,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2923,10 +2922,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596232</v>
+        <v>596323</v>
       </c>
       <c r="R21" t="n">
-        <v>6924082</v>
+        <v>6924104</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2958,7 +2957,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2968,7 +2967,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2995,10 +2994,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124927907</v>
+        <v>124927331</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3007,30 +3006,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596183</v>
+        <v>596228</v>
       </c>
       <c r="R22" t="n">
-        <v>6924165</v>
+        <v>6924195</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3111,10 +3111,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124925523</v>
+        <v>124928235</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>56722</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3123,38 +3123,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596346</v>
+        <v>596183</v>
       </c>
       <c r="R23" t="n">
-        <v>6924199</v>
+        <v>6924165</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3186,7 +3191,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3196,7 +3201,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,22 +3216,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124926296</v>
+        <v>124929949</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3239,39 +3244,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596339</v>
+        <v>596267</v>
       </c>
       <c r="R24" t="n">
-        <v>6924185</v>
+        <v>6924058</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -2172,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124929444</v>
+        <v>124926902</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,34 +2188,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596259</v>
+        <v>596234</v>
       </c>
       <c r="R15" t="n">
-        <v>6924079</v>
+        <v>6924156</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2262,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,22 +2282,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124926902</v>
+        <v>124929444</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,39 +2310,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596234</v>
+        <v>596259</v>
       </c>
       <c r="R16" t="n">
-        <v>6924156</v>
+        <v>6924079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,12 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,12 +2394,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124930808</v>
+        <v>124929949</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,43 +1370,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596344</v>
+        <v>596267</v>
       </c>
       <c r="R8" t="n">
-        <v>6924086</v>
+        <v>6924058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124925426</v>
+        <v>124931273</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,21 +1486,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1515,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596395</v>
+        <v>596323</v>
       </c>
       <c r="R9" t="n">
-        <v>6924217</v>
+        <v>6924104</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,7 +1545,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1555,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124928083</v>
+        <v>124931177</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,31 +1594,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1632,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596173</v>
+        <v>596344</v>
       </c>
       <c r="R10" t="n">
-        <v>6924184</v>
+        <v>6924086</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1672,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124925523</v>
+        <v>124927907</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,38 +1838,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596346</v>
+        <v>596183</v>
       </c>
       <c r="R12" t="n">
-        <v>6924199</v>
+        <v>6924165</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,22 +1930,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124927193</v>
+        <v>124927331</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,43 +1954,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596249</v>
+        <v>596228</v>
       </c>
       <c r="R13" t="n">
-        <v>6924197</v>
+        <v>6924195</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,12 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,22 +2047,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124929330</v>
+        <v>124930808</v>
       </c>
       <c r="B14" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,34 +2075,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596232</v>
+        <v>596344</v>
       </c>
       <c r="R14" t="n">
-        <v>6924082</v>
+        <v>6924086</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,10 +2176,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124926902</v>
+        <v>124925523</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,39 +2192,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596234</v>
+        <v>596346</v>
       </c>
       <c r="R15" t="n">
-        <v>6924156</v>
+        <v>6924199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,12 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,22 +2276,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124929444</v>
+        <v>124931729</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,34 +2304,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596259</v>
+        <v>596350</v>
       </c>
       <c r="R16" t="n">
-        <v>6924079</v>
+        <v>6924076</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2369,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,22 +2397,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124927907</v>
+        <v>124925426</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,42 +2421,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596183</v>
+        <v>596395</v>
       </c>
       <c r="R17" t="n">
-        <v>6924165</v>
+        <v>6924217</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2485,7 +2484,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2495,7 +2494,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2510,22 +2509,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124931729</v>
+        <v>124929330</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>96979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2534,47 +2533,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596350</v>
+        <v>596232</v>
       </c>
       <c r="R18" t="n">
-        <v>6924076</v>
+        <v>6924082</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2596,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2606,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,19 +2621,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124931177</v>
+        <v>124926902</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2679,19 +2669,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596344</v>
+        <v>596234</v>
       </c>
       <c r="R19" t="n">
-        <v>6924086</v>
+        <v>6924156</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2723,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,12 +2723,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2753,22 +2743,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124926296</v>
+        <v>124929444</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2781,39 +2771,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596339</v>
+        <v>596259</v>
       </c>
       <c r="R20" t="n">
-        <v>6924185</v>
+        <v>6924079</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2845,7 +2830,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2855,7 +2840,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,10 +2867,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124931273</v>
+        <v>124926296</v>
       </c>
       <c r="B21" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2894,38 +2879,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596323</v>
+        <v>596339</v>
       </c>
       <c r="R21" t="n">
-        <v>6924104</v>
+        <v>6924185</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2994,7 +2984,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124927331</v>
+        <v>124928083</v>
       </c>
       <c r="B22" t="n">
         <v>56722</v>
@@ -3039,10 +3029,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596228</v>
+        <v>596173</v>
       </c>
       <c r="R22" t="n">
-        <v>6924195</v>
+        <v>6924184</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,7 +3064,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3084,7 +3074,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,12 +3089,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3228,10 +3218,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124929949</v>
+        <v>124927193</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3244,34 +3234,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596267</v>
+        <v>596249</v>
       </c>
       <c r="R24" t="n">
-        <v>6924058</v>
+        <v>6924197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3303,7 +3298,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3308,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3328,12 +3328,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -3101,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124928235</v>
+        <v>124927193</v>
       </c>
       <c r="B23" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3113,43 +3113,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596183</v>
+        <v>596249</v>
       </c>
       <c r="R23" t="n">
-        <v>6924165</v>
+        <v>6924197</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3191,7 +3191,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3206,22 +3211,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124927193</v>
+        <v>124928235</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3230,43 +3235,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596249</v>
+        <v>596183</v>
       </c>
       <c r="R24" t="n">
-        <v>6924197</v>
+        <v>6924165</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3298,7 +3303,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3308,12 +3313,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3328,12 +3328,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328828</v>
+        <v>124328603</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -946,7 +946,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -985,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124326926</v>
+        <v>124329435</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,34 +1038,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Spår 3 tecken hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596167</v>
+        <v>596198</v>
       </c>
       <c r="R5" t="n">
-        <v>6924177</v>
+        <v>6924172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,9 +1103,19 @@
           <t>2025-04-22</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124329435</v>
+        <v>124326926</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,42 +1158,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spår 3 tecken hackspett , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596198</v>
+        <v>596167</v>
       </c>
       <c r="R6" t="n">
-        <v>6924172</v>
+        <v>6924177</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,19 +1215,9 @@
           <t>2025-04-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124929949</v>
+        <v>124927907</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,38 +1370,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596267</v>
+        <v>596183</v>
       </c>
       <c r="R8" t="n">
-        <v>6924058</v>
+        <v>6924165</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,22 +1462,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124931273</v>
+        <v>124927157</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,38 +1486,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596323</v>
+        <v>596290</v>
       </c>
       <c r="R9" t="n">
-        <v>6924104</v>
+        <v>6924176</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,7 +1564,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124931177</v>
+        <v>124929949</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,39 +1612,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596344</v>
+        <v>596267</v>
       </c>
       <c r="R10" t="n">
-        <v>6924086</v>
+        <v>6924058</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,12 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124927157</v>
+        <v>124929330</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,43 +1720,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596290</v>
+        <v>596232</v>
       </c>
       <c r="R11" t="n">
-        <v>6924176</v>
+        <v>6924082</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,12 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,22 +1808,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124927907</v>
+        <v>124931729</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,42 +1832,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596183</v>
+        <v>596350</v>
       </c>
       <c r="R12" t="n">
-        <v>6924165</v>
+        <v>6924076</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,22 +1929,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124927331</v>
+        <v>124931177</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,31 +1953,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1987,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596228</v>
+        <v>596344</v>
       </c>
       <c r="R13" t="n">
-        <v>6924195</v>
+        <v>6924086</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2031,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,22 +2051,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124930808</v>
+        <v>124927193</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,43 +2075,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596344</v>
+        <v>596249</v>
       </c>
       <c r="R14" t="n">
-        <v>6924086</v>
+        <v>6924197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2143,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2153,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,12 +2173,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2288,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124931729</v>
+        <v>124927331</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,47 +2309,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596350</v>
+        <v>596228</v>
       </c>
       <c r="R16" t="n">
-        <v>6924076</v>
+        <v>6924195</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2387,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,22 +2402,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124925426</v>
+        <v>124931273</v>
       </c>
       <c r="B17" t="n">
-        <v>96979</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,21 +2430,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596395</v>
+        <v>596323</v>
       </c>
       <c r="R17" t="n">
-        <v>6924217</v>
+        <v>6924104</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,10 +2526,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124929330</v>
+        <v>124928235</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,34 +2542,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596232</v>
+        <v>596183</v>
       </c>
       <c r="R18" t="n">
-        <v>6924082</v>
+        <v>6924165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2596,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2606,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,12 +2631,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2755,10 +2765,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124929444</v>
+        <v>124928083</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2767,38 +2777,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596259</v>
+        <v>596173</v>
       </c>
       <c r="R20" t="n">
-        <v>6924079</v>
+        <v>6924184</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2830,7 +2845,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2840,7 +2855,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2867,10 +2882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124926296</v>
+        <v>124930808</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2879,31 +2894,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2912,10 +2927,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596339</v>
+        <v>596344</v>
       </c>
       <c r="R21" t="n">
-        <v>6924185</v>
+        <v>6924086</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2962,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2972,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2999,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124928083</v>
+        <v>124925426</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3000,39 +3015,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596173</v>
+        <v>596395</v>
       </c>
       <c r="R22" t="n">
-        <v>6924184</v>
+        <v>6924217</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3064,7 +3074,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3074,7 +3084,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3101,10 +3111,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124927193</v>
+        <v>124929444</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3117,39 +3127,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596249</v>
+        <v>596259</v>
       </c>
       <c r="R23" t="n">
-        <v>6924197</v>
+        <v>6924079</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3181,7 +3186,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3191,12 +3196,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,22 +3211,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124928235</v>
+        <v>124926296</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3235,31 +3235,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596183</v>
+        <v>596339</v>
       </c>
       <c r="R24" t="n">
-        <v>6924165</v>
+        <v>6924185</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3328,12 +3328,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328603</v>
+        <v>124328828</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -946,7 +946,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -985,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124329435</v>
+        <v>124326926</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,42 +1038,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spår 3 tecken hackspett , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596198</v>
+        <v>596167</v>
       </c>
       <c r="R5" t="n">
-        <v>6924172</v>
+        <v>6924177</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,19 +1095,9 @@
           <t>2025-04-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1112,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124326926</v>
+        <v>124329435</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,34 +1140,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Spår 3 tecken hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596167</v>
+        <v>596198</v>
       </c>
       <c r="R6" t="n">
-        <v>6924177</v>
+        <v>6924172</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,9 +1205,19 @@
           <t>2025-04-22</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124927907</v>
+        <v>124927331</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,30 +1370,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596183</v>
+        <v>596228</v>
       </c>
       <c r="R8" t="n">
-        <v>6924165</v>
+        <v>6924195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124927157</v>
+        <v>124930808</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,43 +1487,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596290</v>
+        <v>596344</v>
       </c>
       <c r="R9" t="n">
-        <v>6924176</v>
+        <v>6924086</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,12 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,22 +1580,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124929949</v>
+        <v>124928083</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,38 +1604,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596267</v>
+        <v>596173</v>
       </c>
       <c r="R10" t="n">
-        <v>6924058</v>
+        <v>6924184</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1682,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124929330</v>
+        <v>124929949</v>
       </c>
       <c r="B11" t="n">
-        <v>96979</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,25 +1721,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1749,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596232</v>
+        <v>596267</v>
       </c>
       <c r="R11" t="n">
-        <v>6924082</v>
+        <v>6924058</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124931729</v>
+        <v>124926296</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,43 +1837,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596350</v>
+        <v>596339</v>
       </c>
       <c r="R12" t="n">
-        <v>6924076</v>
+        <v>6924185</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,12 +1926,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2063,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124927193</v>
+        <v>124931273</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,43 +2072,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596249</v>
+        <v>596323</v>
       </c>
       <c r="R14" t="n">
-        <v>6924197</v>
+        <v>6924104</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2153,12 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,22 +2160,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124925523</v>
+        <v>124927157</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2201,34 +2188,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596346</v>
+        <v>596290</v>
       </c>
       <c r="R15" t="n">
-        <v>6924199</v>
+        <v>6924176</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2260,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2262,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,19 +2282,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124927331</v>
+        <v>124928235</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2333,7 +2330,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2342,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596228</v>
+        <v>596183</v>
       </c>
       <c r="R16" t="n">
-        <v>6924195</v>
+        <v>6924165</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124931273</v>
+        <v>124925523</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2426,38 +2423,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596323</v>
+        <v>596346</v>
       </c>
       <c r="R17" t="n">
-        <v>6924104</v>
+        <v>6924199</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,22 +2511,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124928235</v>
+        <v>124926902</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2538,43 +2535,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596183</v>
+        <v>596234</v>
       </c>
       <c r="R18" t="n">
-        <v>6924165</v>
+        <v>6924156</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2613,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,22 +2633,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124926902</v>
+        <v>124925426</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2655,43 +2657,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596234</v>
+        <v>596395</v>
       </c>
       <c r="R19" t="n">
-        <v>6924156</v>
+        <v>6924217</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2723,7 +2720,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,12 +2730,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2753,22 +2745,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124928083</v>
+        <v>124929444</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2777,43 +2769,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596173</v>
+        <v>596259</v>
       </c>
       <c r="R20" t="n">
-        <v>6924184</v>
+        <v>6924079</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2845,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2855,7 +2842,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124930808</v>
+        <v>124929330</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2898,39 +2885,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596344</v>
+        <v>596232</v>
       </c>
       <c r="R21" t="n">
-        <v>6924086</v>
+        <v>6924082</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2962,7 +2944,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2972,7 +2954,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2999,10 +2981,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124925426</v>
+        <v>124927907</v>
       </c>
       <c r="B22" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3011,38 +2993,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596395</v>
+        <v>596183</v>
       </c>
       <c r="R22" t="n">
-        <v>6924217</v>
+        <v>6924165</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,7 +3060,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3084,7 +3070,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,22 +3085,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124929444</v>
+        <v>124931729</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3127,34 +3113,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596259</v>
+        <v>596350</v>
       </c>
       <c r="R23" t="n">
-        <v>6924079</v>
+        <v>6924076</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3186,7 +3181,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3196,7 +3191,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,22 +3206,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124926296</v>
+        <v>124927193</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3239,16 +3234,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3264,14 +3259,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596339</v>
+        <v>596249</v>
       </c>
       <c r="R24" t="n">
-        <v>6924185</v>
+        <v>6924197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3303,7 +3298,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3308,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3328,12 +3328,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328828</v>
+        <v>124328603</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -946,7 +946,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -985,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124326926</v>
+        <v>124329435</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,34 +1038,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Spår 3 tecken hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596167</v>
+        <v>596198</v>
       </c>
       <c r="R5" t="n">
-        <v>6924177</v>
+        <v>6924172</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,9 +1103,19 @@
           <t>2025-04-22</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124329435</v>
+        <v>124326926</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,42 +1158,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spår 3 tecken hackspett , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596198</v>
+        <v>596167</v>
       </c>
       <c r="R6" t="n">
-        <v>6924172</v>
+        <v>6924177</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,19 +1215,9 @@
           <t>2025-04-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124926296</v>
+        <v>124931177</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,16 +1837,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1857,7 +1857,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596339</v>
+        <v>596344</v>
       </c>
       <c r="R12" t="n">
-        <v>6924185</v>
+        <v>6924086</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1911,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124931177</v>
+        <v>124926296</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,16 +1959,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1974,7 +1979,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1983,10 +1988,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596344</v>
+        <v>596339</v>
       </c>
       <c r="R13" t="n">
-        <v>6924086</v>
+        <v>6924185</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2023,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,12 +2033,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2757,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124929444</v>
+        <v>124929330</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>96979</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2769,25 +2769,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596259</v>
+        <v>596232</v>
       </c>
       <c r="R20" t="n">
-        <v>6924079</v>
+        <v>6924082</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124929330</v>
+        <v>124929444</v>
       </c>
       <c r="B21" t="n">
-        <v>96979</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596232</v>
+        <v>596259</v>
       </c>
       <c r="R21" t="n">
-        <v>6924082</v>
+        <v>6924079</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328603</v>
+        <v>124326926</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,43 +917,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596290</v>
+        <v>596167</v>
       </c>
       <c r="R4" t="n">
-        <v>6924176</v>
+        <v>6924177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,19 +978,9 @@
           <t>2025-04-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,12 +995,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1142,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124326926</v>
+        <v>124328603</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,38 +1139,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596167</v>
+        <v>596290</v>
       </c>
       <c r="R6" t="n">
-        <v>6924177</v>
+        <v>6924176</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,9 +1205,19 @@
           <t>2025-04-22</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,12 +1232,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124930808</v>
+        <v>124931273</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,39 +1491,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596344</v>
+        <v>596323</v>
       </c>
       <c r="R9" t="n">
-        <v>6924086</v>
+        <v>6924104</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1565,7 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124928083</v>
+        <v>124928235</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1628,7 +1623,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1637,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596173</v>
+        <v>596183</v>
       </c>
       <c r="R10" t="n">
-        <v>6924184</v>
+        <v>6924165</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,22 +1692,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124929949</v>
+        <v>124925426</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>96979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,25 +1716,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,10 +1744,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596267</v>
+        <v>596395</v>
       </c>
       <c r="R11" t="n">
-        <v>6924058</v>
+        <v>6924217</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1789,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124931177</v>
+        <v>124929949</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,39 +1832,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596344</v>
+        <v>596267</v>
       </c>
       <c r="R12" t="n">
-        <v>6924086</v>
+        <v>6924058</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1891,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,12 +1901,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,10 +1928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124926296</v>
+        <v>124925523</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,39 +1944,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596339</v>
+        <v>596346</v>
       </c>
       <c r="R13" t="n">
-        <v>6924185</v>
+        <v>6924199</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2033,7 +2013,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,22 +2028,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124931273</v>
+        <v>124927193</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,38 +2052,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596323</v>
+        <v>596249</v>
       </c>
       <c r="R14" t="n">
-        <v>6924104</v>
+        <v>6924197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2130,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,22 +2150,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124927157</v>
+        <v>124926296</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,16 +2178,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2213,14 +2203,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596290</v>
+        <v>596339</v>
       </c>
       <c r="R15" t="n">
-        <v>6924176</v>
+        <v>6924185</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2242,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,12 +2252,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,19 +2267,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124928235</v>
+        <v>124930808</v>
       </c>
       <c r="B16" t="n">
         <v>56722</v>
@@ -2330,7 +2315,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2339,10 +2324,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596183</v>
+        <v>596344</v>
       </c>
       <c r="R16" t="n">
-        <v>6924165</v>
+        <v>6924086</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,22 +2384,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124925523</v>
+        <v>124927907</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,38 +2408,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596346</v>
+        <v>596183</v>
       </c>
       <c r="R17" t="n">
-        <v>6924199</v>
+        <v>6924165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2486,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,22 +2500,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124926902</v>
+        <v>124929330</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,43 +2524,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596234</v>
+        <v>596232</v>
       </c>
       <c r="R18" t="n">
-        <v>6924156</v>
+        <v>6924082</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2603,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,12 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,22 +2612,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124925426</v>
+        <v>124926902</v>
       </c>
       <c r="B19" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2657,38 +2636,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596395</v>
+        <v>596234</v>
       </c>
       <c r="R19" t="n">
-        <v>6924217</v>
+        <v>6924156</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,7 +2704,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2730,7 +2714,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,22 +2734,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124929330</v>
+        <v>124929444</v>
       </c>
       <c r="B20" t="n">
-        <v>96979</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2769,25 +2758,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2797,10 +2786,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596232</v>
+        <v>596259</v>
       </c>
       <c r="R20" t="n">
-        <v>6924082</v>
+        <v>6924079</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,7 +2821,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,7 +2831,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124929444</v>
+        <v>124931729</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,34 +2874,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596259</v>
+        <v>596350</v>
       </c>
       <c r="R21" t="n">
-        <v>6924079</v>
+        <v>6924076</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2944,7 +2942,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2954,7 +2952,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,22 +2967,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124927907</v>
+        <v>124931177</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2993,30 +2991,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3025,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596183</v>
+        <v>596344</v>
       </c>
       <c r="R22" t="n">
-        <v>6924165</v>
+        <v>6924086</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3060,7 +3059,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3070,7 +3069,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,22 +3089,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124931729</v>
+        <v>124927157</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3113,43 +3117,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596350</v>
+        <v>596290</v>
       </c>
       <c r="R23" t="n">
-        <v>6924076</v>
+        <v>6924176</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3191,7 +3191,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3206,22 +3211,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124927193</v>
+        <v>124928083</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3230,43 +3235,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596249</v>
+        <v>596173</v>
       </c>
       <c r="R24" t="n">
-        <v>6924197</v>
+        <v>6924184</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3298,7 +3303,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3308,12 +3313,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3328,12 +3328,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124927331</v>
+        <v>124931729</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,43 +1370,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596228</v>
+        <v>596350</v>
       </c>
       <c r="R8" t="n">
-        <v>6924195</v>
+        <v>6924076</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124931273</v>
+        <v>124929444</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,25 +1491,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1515,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596323</v>
+        <v>596259</v>
       </c>
       <c r="R9" t="n">
-        <v>6924104</v>
+        <v>6924079</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,7 +1591,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124928235</v>
+        <v>124930808</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1623,7 +1627,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1632,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596183</v>
+        <v>596344</v>
       </c>
       <c r="R10" t="n">
-        <v>6924165</v>
+        <v>6924086</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,22 +1696,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124925426</v>
+        <v>124927193</v>
       </c>
       <c r="B11" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,38 +1720,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596395</v>
+        <v>596249</v>
       </c>
       <c r="R11" t="n">
-        <v>6924217</v>
+        <v>6924197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1798,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,22 +1818,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124929949</v>
+        <v>124931273</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,25 +1842,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1856,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596267</v>
+        <v>596323</v>
       </c>
       <c r="R12" t="n">
-        <v>6924058</v>
+        <v>6924104</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1901,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124925523</v>
+        <v>124928083</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,38 +1954,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596346</v>
+        <v>596173</v>
       </c>
       <c r="R13" t="n">
-        <v>6924199</v>
+        <v>6924184</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2013,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,19 +2047,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124927193</v>
+        <v>124926902</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2085,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596249</v>
+        <v>596234</v>
       </c>
       <c r="R14" t="n">
-        <v>6924197</v>
+        <v>6924156</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2150,22 +2169,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124926296</v>
+        <v>124925523</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,39 +2197,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596339</v>
+        <v>596346</v>
       </c>
       <c r="R15" t="n">
-        <v>6924185</v>
+        <v>6924199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2252,7 +2266,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,22 +2281,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124930808</v>
+        <v>124931177</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,31 +2305,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2359,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2383,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124927907</v>
+        <v>124929330</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,42 +2427,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596183</v>
+        <v>596232</v>
       </c>
       <c r="R17" t="n">
-        <v>6924165</v>
+        <v>6924082</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,22 +2515,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124929330</v>
+        <v>124928235</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,34 +2543,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596232</v>
+        <v>596183</v>
       </c>
       <c r="R18" t="n">
-        <v>6924082</v>
+        <v>6924165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,22 +2632,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124926902</v>
+        <v>124927331</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,43 +2656,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596234</v>
+        <v>596228</v>
       </c>
       <c r="R19" t="n">
-        <v>6924156</v>
+        <v>6924195</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2704,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2714,12 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2734,22 +2749,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124929444</v>
+        <v>124927157</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2762,34 +2777,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596259</v>
+        <v>596290</v>
       </c>
       <c r="R20" t="n">
-        <v>6924079</v>
+        <v>6924176</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,7 +2841,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2831,7 +2851,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2846,22 +2871,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124931729</v>
+        <v>124926296</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,43 +2899,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596350</v>
+        <v>596339</v>
       </c>
       <c r="R21" t="n">
-        <v>6924076</v>
+        <v>6924185</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2942,7 +2963,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2952,7 +2973,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2967,22 +2988,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124931177</v>
+        <v>124929949</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2995,39 +3016,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596344</v>
+        <v>596267</v>
       </c>
       <c r="R22" t="n">
-        <v>6924086</v>
+        <v>6924058</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,7 +3075,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3069,12 +3085,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3101,10 +3112,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124927157</v>
+        <v>124927907</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3113,43 +3124,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596290</v>
+        <v>596183</v>
       </c>
       <c r="R23" t="n">
-        <v>6924176</v>
+        <v>6924165</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3181,7 +3191,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3191,12 +3201,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3223,10 +3228,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124928083</v>
+        <v>124925426</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3239,39 +3244,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596173</v>
+        <v>596395</v>
       </c>
       <c r="R24" t="n">
-        <v>6924184</v>
+        <v>6924217</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124931729</v>
+        <v>124926296</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,43 +1374,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596350</v>
+        <v>596339</v>
       </c>
       <c r="R8" t="n">
-        <v>6924076</v>
+        <v>6924185</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1463,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124929444</v>
+        <v>124931729</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,34 +1491,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596259</v>
+        <v>596350</v>
       </c>
       <c r="R9" t="n">
-        <v>6924079</v>
+        <v>6924076</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124930808</v>
+        <v>124931177</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,31 +1608,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1671,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1686,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124927193</v>
+        <v>124927907</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,43 +1730,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596249</v>
+        <v>596183</v>
       </c>
       <c r="R11" t="n">
-        <v>6924197</v>
+        <v>6924165</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,12 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,22 +1822,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124931273</v>
+        <v>124927193</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,38 +1846,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596323</v>
+        <v>596249</v>
       </c>
       <c r="R12" t="n">
-        <v>6924104</v>
+        <v>6924197</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1924,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,19 +1944,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124928083</v>
+        <v>124927331</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1987,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596173</v>
+        <v>596228</v>
       </c>
       <c r="R13" t="n">
-        <v>6924184</v>
+        <v>6924195</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,22 +2061,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124926902</v>
+        <v>124929330</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,43 +2085,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596234</v>
+        <v>596232</v>
       </c>
       <c r="R14" t="n">
-        <v>6924156</v>
+        <v>6924082</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,12 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,12 +2173,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2293,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124931177</v>
+        <v>124931273</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,43 +2309,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596344</v>
+        <v>596323</v>
       </c>
       <c r="R16" t="n">
-        <v>6924086</v>
+        <v>6924104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2373,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,12 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124929330</v>
+        <v>124930808</v>
       </c>
       <c r="B17" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,34 +2425,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596232</v>
+        <v>596344</v>
       </c>
       <c r="R17" t="n">
-        <v>6924082</v>
+        <v>6924086</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2527,10 +2526,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124928235</v>
+        <v>124929444</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,43 +2538,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596183</v>
+        <v>596259</v>
       </c>
       <c r="R18" t="n">
-        <v>6924165</v>
+        <v>6924079</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2607,7 +2601,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,7 +2611,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,22 +2626,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124927331</v>
+        <v>124926902</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2656,43 +2650,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596228</v>
+        <v>596234</v>
       </c>
       <c r="R19" t="n">
-        <v>6924195</v>
+        <v>6924156</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,7 +2718,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2728,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,12 +2748,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2883,10 +2882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124926296</v>
+        <v>124925426</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2895,43 +2894,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596339</v>
+        <v>596395</v>
       </c>
       <c r="R21" t="n">
-        <v>6924185</v>
+        <v>6924217</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2963,7 +2957,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2973,7 +2967,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3000,10 +2994,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124929949</v>
+        <v>124928235</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3012,38 +3006,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596267</v>
+        <v>596183</v>
       </c>
       <c r="R22" t="n">
-        <v>6924058</v>
+        <v>6924165</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3075,7 +3074,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3085,7 +3084,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3100,22 +3099,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124927907</v>
+        <v>124929949</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3124,42 +3123,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596183</v>
+        <v>596267</v>
       </c>
       <c r="R23" t="n">
-        <v>6924165</v>
+        <v>6924058</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3191,7 +3186,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3201,7 +3196,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3216,22 +3211,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124925426</v>
+        <v>124928083</v>
       </c>
       <c r="B24" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3244,34 +3239,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596395</v>
+        <v>596173</v>
       </c>
       <c r="R24" t="n">
-        <v>6924217</v>
+        <v>6924184</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124926296</v>
+        <v>124929949</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,39 +1374,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596339</v>
+        <v>596267</v>
       </c>
       <c r="R8" t="n">
-        <v>6924185</v>
+        <v>6924058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124931729</v>
+        <v>124929330</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,47 +1482,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596350</v>
+        <v>596232</v>
       </c>
       <c r="R9" t="n">
-        <v>6924076</v>
+        <v>6924082</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1545,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1555,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,22 +1570,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124931177</v>
+        <v>124931273</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,43 +1594,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596344</v>
+        <v>596323</v>
       </c>
       <c r="R10" t="n">
-        <v>6924086</v>
+        <v>6924104</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,12 +1667,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124927907</v>
+        <v>124931177</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,30 +1706,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1762,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596183</v>
+        <v>596344</v>
       </c>
       <c r="R11" t="n">
-        <v>6924165</v>
+        <v>6924086</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1784,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,22 +1804,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124927193</v>
+        <v>124928235</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,43 +1828,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596249</v>
+        <v>596183</v>
       </c>
       <c r="R12" t="n">
-        <v>6924197</v>
+        <v>6924165</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,12 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,12 +1921,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2073,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124929330</v>
+        <v>124926296</v>
       </c>
       <c r="B14" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,38 +2062,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596232</v>
+        <v>596339</v>
       </c>
       <c r="R14" t="n">
-        <v>6924082</v>
+        <v>6924185</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2140,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124925523</v>
+        <v>124928083</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,38 +2179,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596346</v>
+        <v>596173</v>
       </c>
       <c r="R15" t="n">
-        <v>6924199</v>
+        <v>6924184</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2260,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,22 +2272,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124931273</v>
+        <v>124925523</v>
       </c>
       <c r="B16" t="n">
-        <v>90977</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,38 +2296,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596323</v>
+        <v>596346</v>
       </c>
       <c r="R16" t="n">
-        <v>6924104</v>
+        <v>6924199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,22 +2384,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124930808</v>
+        <v>124931729</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,43 +2408,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596344</v>
+        <v>596350</v>
       </c>
       <c r="R17" t="n">
-        <v>6924086</v>
+        <v>6924076</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,7 +2480,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2490,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,22 +2505,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124929444</v>
+        <v>124927157</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,34 +2533,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596259</v>
+        <v>596290</v>
       </c>
       <c r="R18" t="n">
-        <v>6924079</v>
+        <v>6924176</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2601,7 +2597,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,7 +2607,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,22 +2627,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124926902</v>
+        <v>124930808</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2650,43 +2651,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596234</v>
+        <v>596344</v>
       </c>
       <c r="R19" t="n">
-        <v>6924156</v>
+        <v>6924086</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2718,7 +2719,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2728,12 +2729,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,22 +2744,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124927157</v>
+        <v>124929444</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2776,39 +2772,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596290</v>
+        <v>596259</v>
       </c>
       <c r="R20" t="n">
-        <v>6924176</v>
+        <v>6924079</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2840,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2850,12 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,22 +2856,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124925426</v>
+        <v>124927907</v>
       </c>
       <c r="B21" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2894,38 +2880,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596395</v>
+        <v>596183</v>
       </c>
       <c r="R21" t="n">
-        <v>6924217</v>
+        <v>6924165</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2982,22 +2972,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124928235</v>
+        <v>124927193</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3006,43 +2996,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596183</v>
+        <v>596249</v>
       </c>
       <c r="R22" t="n">
-        <v>6924165</v>
+        <v>6924197</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,7 +3064,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3084,7 +3074,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,22 +3094,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124929949</v>
+        <v>124926902</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3127,34 +3122,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596267</v>
+        <v>596234</v>
       </c>
       <c r="R23" t="n">
-        <v>6924058</v>
+        <v>6924156</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3196,7 +3196,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,22 +3216,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124928083</v>
+        <v>124925426</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3239,39 +3244,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596173</v>
+        <v>596395</v>
       </c>
       <c r="R24" t="n">
-        <v>6924184</v>
+        <v>6924217</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -2639,10 +2639,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124930808</v>
+        <v>124929444</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2651,43 +2651,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596344</v>
+        <v>596259</v>
       </c>
       <c r="R19" t="n">
-        <v>6924086</v>
+        <v>6924079</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2719,7 +2714,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,7 +2724,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,10 +2751,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124929444</v>
+        <v>124930808</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,38 +2763,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596259</v>
+        <v>596344</v>
       </c>
       <c r="R20" t="n">
-        <v>6924079</v>
+        <v>6924086</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124929949</v>
+        <v>124925523</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,34 +1374,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596267</v>
+        <v>596346</v>
       </c>
       <c r="R8" t="n">
-        <v>6924058</v>
+        <v>6924199</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,22 +1458,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124929330</v>
+        <v>124926296</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,38 +1482,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596232</v>
+        <v>596339</v>
       </c>
       <c r="R9" t="n">
-        <v>6924082</v>
+        <v>6924185</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,7 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124931273</v>
+        <v>124926902</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,38 +1599,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596323</v>
+        <v>596234</v>
       </c>
       <c r="R10" t="n">
-        <v>6924104</v>
+        <v>6924156</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,7 +1677,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,22 +1697,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124931177</v>
+        <v>124927331</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,31 +1721,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1739,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596344</v>
+        <v>596228</v>
       </c>
       <c r="R11" t="n">
-        <v>6924086</v>
+        <v>6924195</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1774,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,12 +1799,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,22 +1814,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124928235</v>
+        <v>124929444</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,43 +1838,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596183</v>
+        <v>596259</v>
       </c>
       <c r="R12" t="n">
-        <v>6924165</v>
+        <v>6924079</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,19 +1926,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124927331</v>
+        <v>124930808</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1978,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596228</v>
+        <v>596344</v>
       </c>
       <c r="R13" t="n">
-        <v>6924195</v>
+        <v>6924086</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,22 +2043,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124926296</v>
+        <v>124929949</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,39 +2071,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596339</v>
+        <v>596267</v>
       </c>
       <c r="R14" t="n">
-        <v>6924185</v>
+        <v>6924058</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,10 +2167,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124928083</v>
+        <v>124927907</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,31 +2179,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2212,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596173</v>
+        <v>596183</v>
       </c>
       <c r="R15" t="n">
-        <v>6924184</v>
+        <v>6924165</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,22 +2271,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124925523</v>
+        <v>124928083</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,38 +2295,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596346</v>
+        <v>596173</v>
       </c>
       <c r="R16" t="n">
-        <v>6924199</v>
+        <v>6924184</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2373,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,22 +2388,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124931729</v>
+        <v>124928235</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,47 +2412,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596350</v>
+        <v>596183</v>
       </c>
       <c r="R17" t="n">
-        <v>6924076</v>
+        <v>6924165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,22 +2505,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124927157</v>
+        <v>124929330</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2529,43 +2529,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596290</v>
+        <v>596232</v>
       </c>
       <c r="R18" t="n">
-        <v>6924176</v>
+        <v>6924082</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2597,7 +2592,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2607,12 +2602,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,22 +2617,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124929444</v>
+        <v>124925426</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>96979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2651,25 +2641,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2679,10 +2669,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596259</v>
+        <v>596395</v>
       </c>
       <c r="R19" t="n">
-        <v>6924079</v>
+        <v>6924217</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,7 +2704,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2724,7 +2714,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2751,10 +2741,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124930808</v>
+        <v>124931177</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2763,31 +2753,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2831,7 +2821,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2831,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,10 +2863,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124927907</v>
+        <v>124931729</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,42 +2875,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596183</v>
+        <v>596350</v>
       </c>
       <c r="R21" t="n">
-        <v>6924165</v>
+        <v>6924076</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,19 +2972,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124927193</v>
+        <v>124927157</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -3025,14 +3025,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596249</v>
+        <v>596290</v>
       </c>
       <c r="R22" t="n">
-        <v>6924197</v>
+        <v>6924176</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3094,22 +3094,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124926902</v>
+        <v>124931273</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3118,43 +3118,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596234</v>
+        <v>596323</v>
       </c>
       <c r="R23" t="n">
-        <v>6924156</v>
+        <v>6924104</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3186,7 +3181,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3196,12 +3191,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3216,22 +3206,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124925426</v>
+        <v>124927193</v>
       </c>
       <c r="B24" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3240,38 +3230,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596395</v>
+        <v>596249</v>
       </c>
       <c r="R24" t="n">
-        <v>6924217</v>
+        <v>6924197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3303,7 +3298,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3308,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3328,12 +3328,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1247,7 +1247,7 @@
         <v>124664148</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124925523</v>
+        <v>124925426</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>97147</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,38 +1370,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596346</v>
+        <v>596395</v>
       </c>
       <c r="R8" t="n">
-        <v>6924199</v>
+        <v>6924217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,22 +1458,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124926296</v>
+        <v>124927331</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>56836</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,31 +1482,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596339</v>
+        <v>596228</v>
       </c>
       <c r="R9" t="n">
-        <v>6924185</v>
+        <v>6924195</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,22 +1575,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124926902</v>
+        <v>124927157</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,14 +1628,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596234</v>
+        <v>596290</v>
       </c>
       <c r="R10" t="n">
-        <v>6924156</v>
+        <v>6924176</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,22 +1697,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124927331</v>
+        <v>124927193</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,43 +1721,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596228</v>
+        <v>596249</v>
       </c>
       <c r="R11" t="n">
-        <v>6924195</v>
+        <v>6924197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,7 +1799,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,22 +1819,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124929444</v>
+        <v>124926902</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,34 +1847,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596259</v>
+        <v>596234</v>
       </c>
       <c r="R12" t="n">
-        <v>6924079</v>
+        <v>6924156</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1911,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1921,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,22 +1941,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124930808</v>
+        <v>124929949</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>80028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,43 +1965,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596344</v>
+        <v>596267</v>
       </c>
       <c r="R13" t="n">
-        <v>6924086</v>
+        <v>6924058</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2028,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2038,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124929949</v>
+        <v>124928083</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>56836</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,38 +2077,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596267</v>
+        <v>596173</v>
       </c>
       <c r="R14" t="n">
-        <v>6924058</v>
+        <v>6924184</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124927907</v>
+        <v>124929444</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,42 +2194,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596183</v>
+        <v>596259</v>
       </c>
       <c r="R15" t="n">
-        <v>6924165</v>
+        <v>6924079</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,22 +2282,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124928083</v>
+        <v>124925523</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>91184</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,43 +2306,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596173</v>
+        <v>596346</v>
       </c>
       <c r="R16" t="n">
-        <v>6924184</v>
+        <v>6924199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,7 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,22 +2394,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124928235</v>
+        <v>124930808</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2436,7 +2442,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2445,10 +2451,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596183</v>
+        <v>596344</v>
       </c>
       <c r="R17" t="n">
-        <v>6924165</v>
+        <v>6924086</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2480,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2490,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,22 +2511,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124929330</v>
+        <v>124927907</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>98269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2529,38 +2535,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596232</v>
+        <v>596183</v>
       </c>
       <c r="R18" t="n">
-        <v>6924082</v>
+        <v>6924165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2592,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2602,7 +2612,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,22 +2627,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124925426</v>
+        <v>124931729</v>
       </c>
       <c r="B19" t="n">
-        <v>96979</v>
+        <v>57793</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2641,38 +2651,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596395</v>
+        <v>596350</v>
       </c>
       <c r="R19" t="n">
-        <v>6924217</v>
+        <v>6924076</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2704,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2714,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,12 +2748,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2744,7 +2763,7 @@
         <v>124931177</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2863,10 +2882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124931729</v>
+        <v>124928235</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>56836</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2875,47 +2894,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596350</v>
+        <v>596183</v>
       </c>
       <c r="R21" t="n">
-        <v>6924076</v>
+        <v>6924165</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2962,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,7 +2972,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,22 +2987,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124927157</v>
+        <v>124931273</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91131</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2996,43 +3011,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596290</v>
+        <v>596323</v>
       </c>
       <c r="R22" t="n">
-        <v>6924176</v>
+        <v>6924104</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3064,7 +3074,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3074,12 +3084,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3094,22 +3099,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124931273</v>
+        <v>124926296</v>
       </c>
       <c r="B23" t="n">
-        <v>90977</v>
+        <v>57632</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3118,38 +3123,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596323</v>
+        <v>596339</v>
       </c>
       <c r="R23" t="n">
-        <v>6924104</v>
+        <v>6924185</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3181,7 +3191,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3191,7 +3201,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3218,10 +3228,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124927193</v>
+        <v>124929330</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>97147</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3230,43 +3240,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596249</v>
+        <v>596232</v>
       </c>
       <c r="R24" t="n">
-        <v>6924197</v>
+        <v>6924082</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3298,7 +3303,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3308,12 +3313,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3328,12 +3328,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124927193</v>
+        <v>124929949</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,39 +1725,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596249</v>
+        <v>596267</v>
       </c>
       <c r="R11" t="n">
-        <v>6924197</v>
+        <v>6924058</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,12 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,19 +1809,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124926902</v>
+        <v>124927193</v>
       </c>
       <c r="B12" t="n">
         <v>57635</v>
@@ -1876,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596234</v>
+        <v>596249</v>
       </c>
       <c r="R12" t="n">
-        <v>6924156</v>
+        <v>6924197</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1921,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1941,22 +1931,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124929949</v>
+        <v>124926902</v>
       </c>
       <c r="B13" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,34 +1959,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596267</v>
+        <v>596234</v>
       </c>
       <c r="R13" t="n">
-        <v>6924058</v>
+        <v>6924156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,7 +2023,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2038,7 +2033,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,12 +2053,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124925426</v>
+        <v>124929949</v>
       </c>
       <c r="B8" t="n">
-        <v>97147</v>
+        <v>80028</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,25 +1370,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596395</v>
+        <v>596267</v>
       </c>
       <c r="R8" t="n">
-        <v>6924217</v>
+        <v>6924058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124927331</v>
+        <v>124931273</v>
       </c>
       <c r="B9" t="n">
-        <v>56836</v>
+        <v>91131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,39 +1486,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596228</v>
+        <v>596323</v>
       </c>
       <c r="R9" t="n">
-        <v>6924195</v>
+        <v>6924104</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,7 +1545,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1555,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,19 +1570,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124927157</v>
+        <v>124926902</v>
       </c>
       <c r="B10" t="n">
         <v>57635</v>
@@ -1628,14 +1623,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596290</v>
+        <v>596234</v>
       </c>
       <c r="R10" t="n">
-        <v>6924176</v>
+        <v>6924156</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,12 +1672,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,22 +1692,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124929949</v>
+        <v>124928083</v>
       </c>
       <c r="B11" t="n">
-        <v>80028</v>
+        <v>56836</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,38 +1716,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596267</v>
+        <v>596173</v>
       </c>
       <c r="R11" t="n">
-        <v>6924058</v>
+        <v>6924184</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124927193</v>
+        <v>124926296</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,16 +1837,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1862,14 +1862,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596249</v>
+        <v>596339</v>
       </c>
       <c r="R12" t="n">
-        <v>6924197</v>
+        <v>6924185</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,12 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,19 +1926,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124926902</v>
+        <v>124927193</v>
       </c>
       <c r="B13" t="n">
         <v>57635</v>
@@ -1988,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596234</v>
+        <v>596249</v>
       </c>
       <c r="R13" t="n">
-        <v>6924156</v>
+        <v>6924197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2033,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2053,19 +2048,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124928083</v>
+        <v>124930808</v>
       </c>
       <c r="B14" t="n">
         <v>56836</v>
@@ -2110,10 +2105,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596173</v>
+        <v>596344</v>
       </c>
       <c r="R14" t="n">
-        <v>6924184</v>
+        <v>6924086</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,7 +2140,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2150,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124929444</v>
+        <v>124927331</v>
       </c>
       <c r="B15" t="n">
-        <v>80028</v>
+        <v>56836</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,38 +2189,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596259</v>
+        <v>596228</v>
       </c>
       <c r="R15" t="n">
-        <v>6924079</v>
+        <v>6924195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,22 +2282,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124925523</v>
+        <v>124931729</v>
       </c>
       <c r="B16" t="n">
-        <v>91184</v>
+        <v>57793</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,34 +2310,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596346</v>
+        <v>596350</v>
       </c>
       <c r="R16" t="n">
-        <v>6924199</v>
+        <v>6924076</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2369,7 +2378,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2388,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,22 +2403,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124930808</v>
+        <v>124929330</v>
       </c>
       <c r="B17" t="n">
-        <v>56836</v>
+        <v>97147</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,39 +2431,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596344</v>
+        <v>596232</v>
       </c>
       <c r="R17" t="n">
-        <v>6924086</v>
+        <v>6924082</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2486,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2527,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124927907</v>
+        <v>124929444</v>
       </c>
       <c r="B18" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,42 +2539,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596183</v>
+        <v>596259</v>
       </c>
       <c r="R18" t="n">
-        <v>6924165</v>
+        <v>6924079</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,22 +2627,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124931729</v>
+        <v>124927907</v>
       </c>
       <c r="B19" t="n">
-        <v>57793</v>
+        <v>98269</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2651,47 +2651,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596350</v>
+        <v>596183</v>
       </c>
       <c r="R19" t="n">
-        <v>6924076</v>
+        <v>6924165</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2723,7 +2718,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2733,7 +2728,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,19 +2743,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124931177</v>
+        <v>124927157</v>
       </c>
       <c r="B20" t="n">
         <v>57635</v>
@@ -2796,19 +2791,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596344</v>
+        <v>596290</v>
       </c>
       <c r="R20" t="n">
-        <v>6924086</v>
+        <v>6924176</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2840,7 +2835,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2850,12 +2845,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,22 +2865,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124928235</v>
+        <v>124925523</v>
       </c>
       <c r="B21" t="n">
-        <v>56836</v>
+        <v>91184</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2894,43 +2889,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596183</v>
+        <v>596346</v>
       </c>
       <c r="R21" t="n">
-        <v>6924165</v>
+        <v>6924199</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2962,7 +2952,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2972,7 +2962,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,22 +2977,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124931273</v>
+        <v>124931177</v>
       </c>
       <c r="B22" t="n">
-        <v>91131</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3011,38 +3001,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596323</v>
+        <v>596344</v>
       </c>
       <c r="R22" t="n">
-        <v>6924104</v>
+        <v>6924086</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,7 +3069,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3084,7 +3079,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3111,10 +3111,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124926296</v>
+        <v>124928235</v>
       </c>
       <c r="B23" t="n">
-        <v>57632</v>
+        <v>56836</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3123,31 +3123,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596339</v>
+        <v>596183</v>
       </c>
       <c r="R23" t="n">
-        <v>6924185</v>
+        <v>6924165</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3216,19 +3216,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124929330</v>
+        <v>124925426</v>
       </c>
       <c r="B24" t="n">
         <v>97147</v>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596232</v>
+        <v>596395</v>
       </c>
       <c r="R24" t="n">
-        <v>6924082</v>
+        <v>6924217</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -2415,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124929330</v>
+        <v>124929444</v>
       </c>
       <c r="B17" t="n">
-        <v>97147</v>
+        <v>80028</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2427,25 +2427,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596232</v>
+        <v>596259</v>
       </c>
       <c r="R17" t="n">
-        <v>6924082</v>
+        <v>6924079</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2527,10 +2527,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124929444</v>
+        <v>124929330</v>
       </c>
       <c r="B18" t="n">
-        <v>80028</v>
+        <v>97147</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,25 +2539,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596259</v>
+        <v>596232</v>
       </c>
       <c r="R18" t="n">
-        <v>6924079</v>
+        <v>6924082</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2989,10 +2989,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124931177</v>
+        <v>124928235</v>
       </c>
       <c r="B22" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,31 +3001,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596344</v>
+        <v>596183</v>
       </c>
       <c r="R22" t="n">
-        <v>6924086</v>
+        <v>6924165</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3079,12 +3079,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,22 +3094,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124928235</v>
+        <v>124931177</v>
       </c>
       <c r="B23" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3123,31 +3118,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3156,10 +3151,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596183</v>
+        <v>596344</v>
       </c>
       <c r="R23" t="n">
-        <v>6924165</v>
+        <v>6924086</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3191,7 +3186,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3201,7 +3196,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3216,12 +3216,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124931273</v>
+        <v>124928083</v>
       </c>
       <c r="B9" t="n">
-        <v>91131</v>
+        <v>56836</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,34 +1486,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596323</v>
+        <v>596173</v>
       </c>
       <c r="R9" t="n">
-        <v>6924104</v>
+        <v>6924184</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,7 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124926902</v>
+        <v>124931273</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
+        <v>91131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,43 +1599,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596234</v>
+        <v>596323</v>
       </c>
       <c r="R10" t="n">
-        <v>6924156</v>
+        <v>6924104</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,12 +1672,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,22 +1687,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124928083</v>
+        <v>124926902</v>
       </c>
       <c r="B11" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,43 +1711,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596173</v>
+        <v>596234</v>
       </c>
       <c r="R11" t="n">
-        <v>6924184</v>
+        <v>6924156</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1789,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,12 +1809,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1358,15 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124929949</v>
+        <v>124925523</v>
       </c>
       <c r="B8" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,34 +1369,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596267</v>
+        <v>596346</v>
       </c>
       <c r="R8" t="n">
-        <v>6924058</v>
+        <v>6924199</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,27 +1453,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124928083</v>
+        <v>124931273</v>
       </c>
       <c r="B9" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,39 +1476,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596173</v>
+        <v>596323</v>
       </c>
       <c r="R9" t="n">
-        <v>6924184</v>
+        <v>6924104</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,50 +1572,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124931273</v>
+        <v>124926296</v>
       </c>
       <c r="B10" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596323</v>
+        <v>596339</v>
       </c>
       <c r="R10" t="n">
-        <v>6924104</v>
+        <v>6924185</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1647,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,7 +1657,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,11 +1689,6 @@
       <c r="B11" t="n">
         <v>57635</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1821,43 +1801,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124926296</v>
+        <v>124927907</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1866,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596339</v>
+        <v>596183</v>
       </c>
       <c r="R12" t="n">
-        <v>6924185</v>
+        <v>6924165</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,27 +1900,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124927193</v>
+        <v>124931729</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57793</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,27 +1923,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1983,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596249</v>
+        <v>596350</v>
       </c>
       <c r="R13" t="n">
-        <v>6924197</v>
+        <v>6924076</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,12 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,27 +2016,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124930808</v>
+        <v>124925426</v>
       </c>
       <c r="B14" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97147</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,39 +2039,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596344</v>
+        <v>596395</v>
       </c>
       <c r="R14" t="n">
-        <v>6924086</v>
+        <v>6924217</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2150,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,15 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124927331</v>
+        <v>124929330</v>
       </c>
       <c r="B15" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97147</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,39 +2146,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596228</v>
+        <v>596232</v>
       </c>
       <c r="R15" t="n">
-        <v>6924195</v>
+        <v>6924082</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2257,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,71 +2230,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124931729</v>
+        <v>124927331</v>
       </c>
       <c r="B16" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56836</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596350</v>
+        <v>596228</v>
       </c>
       <c r="R16" t="n">
-        <v>6924076</v>
+        <v>6924195</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,7 +2317,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2388,7 +2327,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,12 +2342,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2420,11 +2359,6 @@
       <c r="B17" t="n">
         <v>80028</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2527,15 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124929330</v>
+        <v>124928235</v>
       </c>
       <c r="B18" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56836</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2543,34 +2472,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596232</v>
+        <v>596183</v>
       </c>
       <c r="R18" t="n">
-        <v>6924082</v>
+        <v>6924165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2602,7 +2536,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2612,7 +2546,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,54 +2561,50 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124927907</v>
+        <v>124931177</v>
       </c>
       <c r="B19" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2683,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596183</v>
+        <v>596344</v>
       </c>
       <c r="R19" t="n">
-        <v>6924165</v>
+        <v>6924086</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2718,7 +2648,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2728,7 +2658,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,12 +2678,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2760,11 +2695,6 @@
       <c r="B20" t="n">
         <v>57635</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2877,15 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124925523</v>
+        <v>124927193</v>
       </c>
       <c r="B21" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2893,34 +2818,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596346</v>
+        <v>596249</v>
       </c>
       <c r="R21" t="n">
-        <v>6924199</v>
+        <v>6924197</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2952,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2962,7 +2892,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2989,16 +2924,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124928235</v>
+        <v>124930808</v>
       </c>
       <c r="B22" t="n">
         <v>56836</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>LC</t>
@@ -3025,7 +2955,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3034,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596183</v>
+        <v>596344</v>
       </c>
       <c r="R22" t="n">
-        <v>6924165</v>
+        <v>6924086</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3069,7 +2999,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3079,7 +3009,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3094,27 +3024,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124931177</v>
+        <v>124929949</v>
       </c>
       <c r="B23" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3122,39 +3047,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596344</v>
+        <v>596267</v>
       </c>
       <c r="R23" t="n">
-        <v>6924086</v>
+        <v>6924058</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3186,7 +3106,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3196,12 +3116,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3228,15 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124925426</v>
+        <v>124928083</v>
       </c>
       <c r="B24" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56836</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3244,34 +3154,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596395</v>
+        <v>596173</v>
       </c>
       <c r="R24" t="n">
-        <v>6924217</v>
+        <v>6924184</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3303,7 +3218,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3228,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1010,12 +1010,7 @@
         <v>124329435</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1575,7 +1570,7 @@
         <v>124926296</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>124329435</v>
       </c>
       <c r="B5" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>124926296</v>
       </c>
       <c r="B10" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>124329435</v>
       </c>
       <c r="B5" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>124926296</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>124329435</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>124926296</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>124329435</v>
       </c>
       <c r="B5" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>124926296</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>124329435</v>
       </c>
       <c r="B5" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>124926296</v>
       </c>
       <c r="B10" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1682,7 +1682,7 @@
         <v>124926902</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>124931177</v>
       </c>
       <c r="B19" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>124927157</v>
       </c>
       <c r="B20" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>124927193</v>
       </c>
       <c r="B21" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -1682,7 +1682,7 @@
         <v>124926902</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>124931177</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>124927157</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>124927193</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -3250,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132921980</v>
+        <v>132921994</v>
       </c>
       <c r="B25" t="n">
-        <v>80438</v>
+        <v>92338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,21 +3261,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6040186</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596232</v>
+        <v>596258</v>
       </c>
       <c r="R25" t="n">
-        <v>6924120</v>
+        <v>6924175</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3315,22 +3315,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,6 +3339,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3357,32 +3358,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132921984</v>
+        <v>132921980</v>
       </c>
       <c r="B26" t="n">
-        <v>75433</v>
+        <v>80438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3392,10 +3393,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596383</v>
+        <v>596232</v>
       </c>
       <c r="R26" t="n">
-        <v>6924174</v>
+        <v>6924120</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3427,7 +3428,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3437,7 +3438,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,7 +3465,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132921985</v>
+        <v>132921984</v>
       </c>
       <c r="B27" t="n">
         <v>75433</v>
@@ -3499,10 +3500,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>596387</v>
+        <v>596383</v>
       </c>
       <c r="R27" t="n">
-        <v>6924182</v>
+        <v>6924174</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3534,7 +3535,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3544,7 +3545,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3571,32 +3572,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132921994</v>
+        <v>132921985</v>
       </c>
       <c r="B28" t="n">
-        <v>92338</v>
+        <v>75433</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6040186</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596258</v>
+        <v>596387</v>
       </c>
       <c r="R28" t="n">
-        <v>6924175</v>
+        <v>6924182</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3636,22 +3637,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3660,7 +3661,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4146,10 +4146,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132921978</v>
+        <v>132921965</v>
       </c>
       <c r="B33" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4157,21 +4157,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596210</v>
+        <v>596255</v>
       </c>
       <c r="R33" t="n">
-        <v>6924094</v>
+        <v>6924162</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4211,22 +4211,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4253,10 +4253,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132921965</v>
+        <v>132921978</v>
       </c>
       <c r="B34" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4264,21 +4264,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596255</v>
+        <v>596210</v>
       </c>
       <c r="R34" t="n">
-        <v>6924162</v>
+        <v>6924094</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4318,22 +4318,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -3250,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132921994</v>
+        <v>132921979</v>
       </c>
       <c r="B25" t="n">
-        <v>92338</v>
+        <v>79365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,21 +3261,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596258</v>
+        <v>596219</v>
       </c>
       <c r="R25" t="n">
-        <v>6924175</v>
+        <v>6924101</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3315,22 +3315,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,7 +3339,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3679,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132921979</v>
+        <v>132921994</v>
       </c>
       <c r="B29" t="n">
-        <v>79365</v>
+        <v>92338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3690,21 +3689,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6040186</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3714,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596219</v>
+        <v>596258</v>
       </c>
       <c r="R29" t="n">
-        <v>6924101</v>
+        <v>6924175</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3744,22 +3743,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3768,6 +3767,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -3250,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132921979</v>
+        <v>132921994</v>
       </c>
       <c r="B25" t="n">
-        <v>79365</v>
+        <v>92338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,21 +3261,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6040186</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596219</v>
+        <v>596258</v>
       </c>
       <c r="R25" t="n">
-        <v>6924101</v>
+        <v>6924175</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3315,22 +3315,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,6 +3339,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3678,10 +3679,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132921994</v>
+        <v>132921979</v>
       </c>
       <c r="B29" t="n">
-        <v>92338</v>
+        <v>79365</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,21 +3690,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6040186</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3713,10 +3714,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596258</v>
+        <v>596219</v>
       </c>
       <c r="R29" t="n">
-        <v>6924175</v>
+        <v>6924101</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3743,22 +3744,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,7 +3768,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4146,10 +4146,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132921965</v>
+        <v>132921978</v>
       </c>
       <c r="B33" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4157,21 +4157,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596255</v>
+        <v>596210</v>
       </c>
       <c r="R33" t="n">
-        <v>6924162</v>
+        <v>6924094</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4211,22 +4211,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4253,10 +4253,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132921978</v>
+        <v>132921965</v>
       </c>
       <c r="B34" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4264,21 +4264,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596210</v>
+        <v>596255</v>
       </c>
       <c r="R34" t="n">
-        <v>6924094</v>
+        <v>6924162</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4318,22 +4318,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4806,10 +4806,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132921969</v>
+        <v>132921982</v>
       </c>
       <c r="B39" t="n">
-        <v>79365</v>
+        <v>80438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4817,21 +4817,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4841,10 +4841,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596029</v>
+        <v>596355</v>
       </c>
       <c r="R39" t="n">
-        <v>6924204</v>
+        <v>6924159</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4913,10 +4913,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132921982</v>
+        <v>132921969</v>
       </c>
       <c r="B40" t="n">
-        <v>80438</v>
+        <v>79365</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4924,21 +4924,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596355</v>
+        <v>596029</v>
       </c>
       <c r="R40" t="n">
-        <v>6924159</v>
+        <v>6924204</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5354,10 +5354,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132921967</v>
+        <v>132921973</v>
       </c>
       <c r="B44" t="n">
-        <v>91932</v>
+        <v>57958</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5365,37 +5365,45 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596336</v>
+        <v>596134</v>
       </c>
       <c r="R44" t="n">
-        <v>6924145</v>
+        <v>6924194</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5419,22 +5427,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5461,10 +5474,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132921973</v>
+        <v>132921967</v>
       </c>
       <c r="B45" t="n">
-        <v>57958</v>
+        <v>91932</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5472,45 +5485,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>596134</v>
+        <v>596336</v>
       </c>
       <c r="R45" t="n">
-        <v>6924194</v>
+        <v>6924145</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5534,27 +5539,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -4467,10 +4467,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132921966</v>
+        <v>132921963</v>
       </c>
       <c r="B36" t="n">
-        <v>83181</v>
+        <v>57958</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4478,37 +4478,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596320</v>
+        <v>596161</v>
       </c>
       <c r="R36" t="n">
-        <v>6924149</v>
+        <v>6924185</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4537,7 +4545,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4547,7 +4555,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Kan vara årsfärska</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4574,10 +4587,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132921963</v>
+        <v>132921966</v>
       </c>
       <c r="B37" t="n">
-        <v>57958</v>
+        <v>83181</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4585,45 +4598,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596161</v>
+        <v>596320</v>
       </c>
       <c r="R37" t="n">
-        <v>6924185</v>
+        <v>6924149</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4652,7 +4657,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4662,12 +4667,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Kan vara årsfärska</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -3250,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132921994</v>
+        <v>132921980</v>
       </c>
       <c r="B25" t="n">
-        <v>92338</v>
+        <v>80438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3261,21 +3261,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596258</v>
+        <v>596232</v>
       </c>
       <c r="R25" t="n">
-        <v>6924175</v>
+        <v>6924120</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3315,22 +3315,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,7 +3339,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3358,32 +3357,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132921980</v>
+        <v>132921984</v>
       </c>
       <c r="B26" t="n">
-        <v>80438</v>
+        <v>75433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3393,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596232</v>
+        <v>596383</v>
       </c>
       <c r="R26" t="n">
-        <v>6924120</v>
+        <v>6924174</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3428,7 +3427,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3438,7 +3437,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3465,7 +3464,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132921984</v>
+        <v>132921985</v>
       </c>
       <c r="B27" t="n">
         <v>75433</v>
@@ -3500,10 +3499,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>596383</v>
+        <v>596387</v>
       </c>
       <c r="R27" t="n">
-        <v>6924174</v>
+        <v>6924182</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3535,7 +3534,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3545,7 +3544,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,32 +3571,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132921985</v>
+        <v>132921979</v>
       </c>
       <c r="B28" t="n">
-        <v>75433</v>
+        <v>79365</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3607,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596387</v>
+        <v>596219</v>
       </c>
       <c r="R28" t="n">
-        <v>6924182</v>
+        <v>6924101</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3642,7 +3641,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3652,7 +3651,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3679,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132921979</v>
+        <v>132921994</v>
       </c>
       <c r="B29" t="n">
-        <v>79365</v>
+        <v>92338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3690,21 +3689,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6040186</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3714,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596219</v>
+        <v>596258</v>
       </c>
       <c r="R29" t="n">
-        <v>6924101</v>
+        <v>6924175</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3744,22 +3743,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3768,6 +3767,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132921963</v>
+        <v>132921966</v>
       </c>
       <c r="B36" t="n">
-        <v>57958</v>
+        <v>83181</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4478,45 +4478,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596161</v>
+        <v>596320</v>
       </c>
       <c r="R36" t="n">
-        <v>6924185</v>
+        <v>6924149</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4545,7 +4537,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4555,12 +4547,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Kan vara årsfärska</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4587,10 +4574,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132921966</v>
+        <v>132921963</v>
       </c>
       <c r="B37" t="n">
-        <v>83181</v>
+        <v>57958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4598,37 +4585,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596320</v>
+        <v>596161</v>
       </c>
       <c r="R37" t="n">
-        <v>6924149</v>
+        <v>6924185</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4657,7 +4652,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4667,7 +4662,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Kan vara årsfärska</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4806,10 +4806,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132921982</v>
+        <v>132921969</v>
       </c>
       <c r="B39" t="n">
-        <v>80438</v>
+        <v>79365</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4817,21 +4817,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4841,10 +4841,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596355</v>
+        <v>596029</v>
       </c>
       <c r="R39" t="n">
-        <v>6924159</v>
+        <v>6924204</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4913,10 +4913,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132921969</v>
+        <v>132921982</v>
       </c>
       <c r="B40" t="n">
-        <v>79365</v>
+        <v>80438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4924,21 +4924,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596029</v>
+        <v>596355</v>
       </c>
       <c r="R40" t="n">
-        <v>6924204</v>
+        <v>6924159</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5474,10 +5474,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132921967</v>
+        <v>132921977</v>
       </c>
       <c r="B45" t="n">
-        <v>91932</v>
+        <v>57958</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5485,37 +5485,45 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>596336</v>
+        <v>596162</v>
       </c>
       <c r="R45" t="n">
-        <v>6924145</v>
+        <v>6924158</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5539,22 +5547,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5581,10 +5594,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132921977</v>
+        <v>132921967</v>
       </c>
       <c r="B46" t="n">
-        <v>57958</v>
+        <v>91932</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5592,45 +5605,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>596162</v>
+        <v>596336</v>
       </c>
       <c r="R46" t="n">
-        <v>6924158</v>
+        <v>6924145</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5654,27 +5659,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -5354,10 +5354,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132921973</v>
+        <v>132921967</v>
       </c>
       <c r="B44" t="n">
-        <v>57958</v>
+        <v>91932</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5365,45 +5365,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596134</v>
+        <v>596336</v>
       </c>
       <c r="R44" t="n">
-        <v>6924194</v>
+        <v>6924145</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5427,27 +5419,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5474,7 +5461,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132921977</v>
+        <v>132921973</v>
       </c>
       <c r="B45" t="n">
         <v>57958</v>
@@ -5517,10 +5504,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>596162</v>
+        <v>596134</v>
       </c>
       <c r="R45" t="n">
-        <v>6924158</v>
+        <v>6924194</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5552,7 +5539,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5562,12 +5549,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5594,10 +5581,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132921967</v>
+        <v>132921977</v>
       </c>
       <c r="B46" t="n">
-        <v>91932</v>
+        <v>57958</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,37 +5592,45 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>596336</v>
+        <v>596162</v>
       </c>
       <c r="R46" t="n">
-        <v>6924145</v>
+        <v>6924158</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5659,22 +5654,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -3253,7 +3253,7 @@
         <v>132921980</v>
       </c>
       <c r="B25" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>132921979</v>
       </c>
       <c r="B28" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>132921994</v>
       </c>
       <c r="B29" t="n">
-        <v>92338</v>
+        <v>92340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>132921978</v>
       </c>
       <c r="B33" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>132921965</v>
       </c>
       <c r="B34" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>132921981</v>
       </c>
       <c r="B35" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132921966</v>
+        <v>132921963</v>
       </c>
       <c r="B36" t="n">
-        <v>83181</v>
+        <v>57958</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4478,37 +4478,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596320</v>
+        <v>596161</v>
       </c>
       <c r="R36" t="n">
-        <v>6924149</v>
+        <v>6924185</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4537,7 +4545,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4547,7 +4555,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Kan vara årsfärska</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4574,10 +4587,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132921963</v>
+        <v>132921966</v>
       </c>
       <c r="B37" t="n">
-        <v>57958</v>
+        <v>83182</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4585,45 +4598,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596161</v>
+        <v>596320</v>
       </c>
       <c r="R37" t="n">
-        <v>6924185</v>
+        <v>6924149</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4652,7 +4657,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4662,12 +4667,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Kan vara årsfärska</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4697,7 +4697,7 @@
         <v>132921968</v>
       </c>
       <c r="B38" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4806,10 +4806,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132921969</v>
+        <v>132921982</v>
       </c>
       <c r="B39" t="n">
-        <v>79365</v>
+        <v>80439</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4817,21 +4817,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4841,10 +4841,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596029</v>
+        <v>596355</v>
       </c>
       <c r="R39" t="n">
-        <v>6924204</v>
+        <v>6924159</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4913,10 +4913,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132921982</v>
+        <v>132921969</v>
       </c>
       <c r="B40" t="n">
-        <v>80438</v>
+        <v>79366</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4924,21 +4924,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596355</v>
+        <v>596029</v>
       </c>
       <c r="R40" t="n">
-        <v>6924159</v>
+        <v>6924204</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5023,7 +5023,7 @@
         <v>132921970</v>
       </c>
       <c r="B41" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>132921995</v>
       </c>
       <c r="B43" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>132921967</v>
       </c>
       <c r="B44" t="n">
-        <v>91932</v>
+        <v>91934</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -4467,10 +4467,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132921963</v>
+        <v>132921966</v>
       </c>
       <c r="B36" t="n">
-        <v>57958</v>
+        <v>83182</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4478,45 +4478,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596161</v>
+        <v>596320</v>
       </c>
       <c r="R36" t="n">
-        <v>6924185</v>
+        <v>6924149</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4545,7 +4537,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4555,12 +4547,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Kan vara årsfärska</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4587,10 +4574,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132921966</v>
+        <v>132921963</v>
       </c>
       <c r="B37" t="n">
-        <v>83182</v>
+        <v>57958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4598,37 +4585,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596320</v>
+        <v>596161</v>
       </c>
       <c r="R37" t="n">
-        <v>6924149</v>
+        <v>6924185</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4657,7 +4652,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4667,7 +4662,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Kan vara årsfärska</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5354,10 +5354,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132921967</v>
+        <v>132921973</v>
       </c>
       <c r="B44" t="n">
-        <v>91934</v>
+        <v>57958</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5365,37 +5365,45 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596336</v>
+        <v>596134</v>
       </c>
       <c r="R44" t="n">
-        <v>6924145</v>
+        <v>6924194</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5419,22 +5427,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5461,7 +5474,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132921973</v>
+        <v>132921977</v>
       </c>
       <c r="B45" t="n">
         <v>57958</v>
@@ -5504,10 +5517,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>596134</v>
+        <v>596162</v>
       </c>
       <c r="R45" t="n">
-        <v>6924194</v>
+        <v>6924158</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5539,7 +5552,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5549,12 +5562,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5581,10 +5594,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132921977</v>
+        <v>132921967</v>
       </c>
       <c r="B46" t="n">
-        <v>57958</v>
+        <v>91934</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5592,45 +5605,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>596162</v>
+        <v>596336</v>
       </c>
       <c r="R46" t="n">
-        <v>6924158</v>
+        <v>6924145</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5654,27 +5659,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -4467,10 +4467,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132921966</v>
+        <v>132921963</v>
       </c>
       <c r="B36" t="n">
-        <v>83182</v>
+        <v>57958</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4478,37 +4478,45 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596320</v>
+        <v>596161</v>
       </c>
       <c r="R36" t="n">
-        <v>6924149</v>
+        <v>6924185</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4537,7 +4545,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4547,7 +4555,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Kan vara årsfärska</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4574,10 +4587,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132921963</v>
+        <v>132921966</v>
       </c>
       <c r="B37" t="n">
-        <v>57958</v>
+        <v>83182</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4585,45 +4598,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596161</v>
+        <v>596320</v>
       </c>
       <c r="R37" t="n">
-        <v>6924185</v>
+        <v>6924149</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4652,7 +4657,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4662,12 +4667,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall. Kan vara årsfärska</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5354,10 +5354,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132921973</v>
+        <v>132921967</v>
       </c>
       <c r="B44" t="n">
-        <v>57958</v>
+        <v>91934</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5365,45 +5365,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596134</v>
+        <v>596336</v>
       </c>
       <c r="R44" t="n">
-        <v>6924194</v>
+        <v>6924145</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5427,27 +5419,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5474,7 +5461,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132921977</v>
+        <v>132921973</v>
       </c>
       <c r="B45" t="n">
         <v>57958</v>
@@ -5517,10 +5504,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>596162</v>
+        <v>596134</v>
       </c>
       <c r="R45" t="n">
-        <v>6924158</v>
+        <v>6924194</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5552,7 +5539,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5562,12 +5549,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5594,10 +5581,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132921967</v>
+        <v>132921977</v>
       </c>
       <c r="B46" t="n">
-        <v>91934</v>
+        <v>57958</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,37 +5592,45 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>596336</v>
+        <v>596162</v>
       </c>
       <c r="R46" t="n">
-        <v>6924145</v>
+        <v>6924158</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5659,22 +5654,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -3681,7 +3681,7 @@
         <v>132921994</v>
       </c>
       <c r="B29" t="n">
-        <v>92340</v>
+        <v>92348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>132921978</v>
       </c>
       <c r="B33" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>132921965</v>
       </c>
       <c r="B34" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>132921981</v>
       </c>
       <c r="B35" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>132921966</v>
       </c>
       <c r="B37" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>132921968</v>
       </c>
       <c r="B38" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>132921995</v>
       </c>
       <c r="B43" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5354,10 +5354,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132921967</v>
+        <v>132921973</v>
       </c>
       <c r="B44" t="n">
-        <v>91934</v>
+        <v>57958</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5365,37 +5365,45 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596336</v>
+        <v>596134</v>
       </c>
       <c r="R44" t="n">
-        <v>6924145</v>
+        <v>6924194</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5419,22 +5427,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5461,7 +5474,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132921973</v>
+        <v>132921977</v>
       </c>
       <c r="B45" t="n">
         <v>57958</v>
@@ -5504,10 +5517,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>596134</v>
+        <v>596162</v>
       </c>
       <c r="R45" t="n">
-        <v>6924194</v>
+        <v>6924158</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5539,7 +5552,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5549,12 +5562,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5581,10 +5594,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132921977</v>
+        <v>132921967</v>
       </c>
       <c r="B46" t="n">
-        <v>57958</v>
+        <v>91942</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5592,45 +5605,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>596162</v>
+        <v>596336</v>
       </c>
       <c r="R46" t="n">
-        <v>6924158</v>
+        <v>6924145</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5654,27 +5659,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118719202</v>
+        <v>132921969</v>
       </c>
       <c r="B2" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Himmelsmyran, väster om, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596246</v>
+        <v>596029</v>
       </c>
       <c r="R2" t="n">
-        <v>6924086</v>
+        <v>6924204</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,82 +766,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>drygt 100-årig blåbärsbarrskog i kant motsumpskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>5 substratenheter # grov sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118719201</v>
+        <v>132921970</v>
       </c>
       <c r="B3" t="n">
-        <v>79603</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Himmelsmyran, väster om, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596246</v>
+        <v>596081</v>
       </c>
       <c r="R3" t="n">
-        <v>6924086</v>
+        <v>6924192</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,44 +873,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>drygt 100-årig blåbärsbarrskog i kant motsumpskog</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>5 substratenheter # grov sälg</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124326926</v>
+        <v>132921979</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596167</v>
+        <v>596219</v>
       </c>
       <c r="R4" t="n">
-        <v>6924177</v>
+        <v>6924101</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,12 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124329435</v>
+        <v>124326926</v>
       </c>
       <c r="B5" t="n">
-        <v>57681</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,42 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spår 3 tecken hackspett , Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596198</v>
+        <v>596167</v>
       </c>
       <c r="R5" t="n">
-        <v>6924172</v>
+        <v>6924177</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,19 +1064,9 @@
           <t>2025-04-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,70 +1081,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124328603</v>
+        <v>132921965</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjäder spillning , Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596290</v>
+        <v>596255</v>
       </c>
       <c r="R6" t="n">
-        <v>6924176</v>
+        <v>6924162</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,22 +1158,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,77 +1188,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124664148</v>
+        <v>132921967</v>
       </c>
       <c r="B7" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596235</v>
+        <v>596336</v>
       </c>
       <c r="R7" t="n">
-        <v>6924189</v>
+        <v>6924145</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,12 +1265,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124925523</v>
+        <v>132921966</v>
       </c>
       <c r="B8" t="n">
-        <v>91184</v>
+        <v>83222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,37 +1318,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596346</v>
+        <v>596320</v>
       </c>
       <c r="R8" t="n">
-        <v>6924199</v>
+        <v>6924149</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,22 +1372,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,44 +1402,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124931273</v>
+        <v>132921968</v>
       </c>
       <c r="B9" t="n">
-        <v>91131</v>
+        <v>83222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,13 +1449,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596323</v>
+        <v>596333</v>
       </c>
       <c r="R9" t="n">
-        <v>6924104</v>
+        <v>6924148</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,22 +1479,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124926296</v>
+        <v>132921978</v>
       </c>
       <c r="B10" t="n">
-        <v>57681</v>
+        <v>83222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,42 +1537,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596339</v>
+        <v>596210</v>
       </c>
       <c r="R10" t="n">
-        <v>6924185</v>
+        <v>6924094</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,22 +1591,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124926902</v>
+        <v>132921981</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>83222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,42 +1644,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596234</v>
+        <v>596306</v>
       </c>
       <c r="R11" t="n">
-        <v>6924156</v>
+        <v>6924187</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,27 +1698,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,64 +1728,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124927907</v>
+        <v>132921995</v>
       </c>
       <c r="B12" t="n">
-        <v>98269</v>
+        <v>83222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596183</v>
+        <v>596284</v>
       </c>
       <c r="R12" t="n">
-        <v>6924165</v>
+        <v>6924197</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,22 +1805,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,22 +1835,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124931729</v>
+        <v>132921996</v>
       </c>
       <c r="B13" t="n">
-        <v>57793</v>
+        <v>83222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,46 +1858,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596350</v>
+        <v>596403</v>
       </c>
       <c r="R13" t="n">
-        <v>6924076</v>
+        <v>6924236</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1981,22 +1912,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2011,22 +1942,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124925426</v>
+        <v>124931273</v>
       </c>
       <c r="B14" t="n">
-        <v>97147</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2058,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596395</v>
+        <v>596323</v>
       </c>
       <c r="R14" t="n">
-        <v>6924217</v>
+        <v>6924104</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2093,7 +2024,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2103,7 +2034,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,32 +2061,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124929330</v>
+        <v>132921984</v>
       </c>
       <c r="B15" t="n">
-        <v>97147</v>
+        <v>75468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,13 +2096,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596232</v>
+        <v>596383</v>
       </c>
       <c r="R15" t="n">
-        <v>6924082</v>
+        <v>6924174</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2195,22 +2126,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,53 +2168,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124927331</v>
+        <v>132921985</v>
       </c>
       <c r="B16" t="n">
-        <v>56836</v>
+        <v>75468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596228</v>
+        <v>596387</v>
       </c>
       <c r="R16" t="n">
-        <v>6924195</v>
+        <v>6924182</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2307,22 +2233,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,22 +2263,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124929444</v>
+        <v>132921997</v>
       </c>
       <c r="B17" t="n">
-        <v>80028</v>
+        <v>75468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2384,13 +2310,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596259</v>
+        <v>596403</v>
       </c>
       <c r="R17" t="n">
-        <v>6924079</v>
+        <v>6924236</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2414,22 +2340,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2456,53 +2382,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124928235</v>
+        <v>132921998</v>
       </c>
       <c r="B18" t="n">
-        <v>56836</v>
+        <v>75468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596183</v>
+        <v>596410</v>
       </c>
       <c r="R18" t="n">
-        <v>6924165</v>
+        <v>6924243</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2526,22 +2447,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2556,22 +2477,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124931177</v>
+        <v>132921999</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>75468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,42 +2500,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596344</v>
+        <v>596412</v>
       </c>
       <c r="R19" t="n">
-        <v>6924086</v>
+        <v>6924247</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2638,27 +2554,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2685,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124927157</v>
+        <v>118719202</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,39 +2607,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tjäder bas, Mpd</t>
+          <t>Himmelsmyran, väster om, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596290</v>
+        <v>596246</v>
       </c>
       <c r="R20" t="n">
-        <v>6924176</v>
+        <v>6924086</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2755,27 +2661,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,26 +2677,39 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>drygt 100-årig blåbärsbarrskog i kant motsumpskog</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>5 substratenheter # grov sälg</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124927193</v>
+        <v>124929444</v>
       </c>
       <c r="B21" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,39 +2717,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hömyran, Hömyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596249</v>
+        <v>596259</v>
       </c>
       <c r="R21" t="n">
-        <v>6924197</v>
+        <v>6924079</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2877,7 +2776,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2887,12 +2786,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2907,62 +2801,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124930808</v>
+        <v>124929949</v>
       </c>
       <c r="B22" t="n">
-        <v>56836</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596344</v>
+        <v>596267</v>
       </c>
       <c r="R22" t="n">
-        <v>6924086</v>
+        <v>6924058</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,7 +2883,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,7 +2893,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,10 +2920,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124929949</v>
+        <v>132921980</v>
       </c>
       <c r="B23" t="n">
-        <v>80028</v>
+        <v>80488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3066,13 +2955,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596267</v>
+        <v>596232</v>
       </c>
       <c r="R23" t="n">
-        <v>6924058</v>
+        <v>6924120</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3096,22 +2985,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3138,53 +3027,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124928083</v>
+        <v>132921982</v>
       </c>
       <c r="B24" t="n">
-        <v>56836</v>
+        <v>80488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596173</v>
+        <v>596355</v>
       </c>
       <c r="R24" t="n">
-        <v>6924184</v>
+        <v>6924159</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3208,22 +3092,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3250,117 +3134,120 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132921980</v>
+        <v>118719201</v>
       </c>
       <c r="B25" t="n">
-        <v>80439</v>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, väster om, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596232</v>
+        <v>596246</v>
       </c>
       <c r="R25" t="n">
-        <v>6924120</v>
+        <v>6924086</v>
       </c>
       <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>drygt 100-årig blåbärsbarrskog i kant motsumpskog</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
         <v>5</v>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Stöde</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>5 substratenheter # grov sälg</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132921984</v>
+        <v>124329435</v>
       </c>
       <c r="B26" t="n">
-        <v>75433</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,37 +3255,45 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Spår 3 tecken hackspett , Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596383</v>
+        <v>596198</v>
       </c>
       <c r="R26" t="n">
-        <v>6924174</v>
+        <v>6924172</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3422,22 +3317,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3452,22 +3347,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132921985</v>
+        <v>124422845</v>
       </c>
       <c r="B27" t="n">
-        <v>75433</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,37 +3370,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>596387</v>
+        <v>596133</v>
       </c>
       <c r="R27" t="n">
-        <v>6924182</v>
+        <v>6924225</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3529,22 +3429,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:36</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:36</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3571,48 +3461,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132921979</v>
+        <v>124926296</v>
       </c>
       <c r="B28" t="n">
-        <v>79366</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596219</v>
+        <v>596339</v>
       </c>
       <c r="R28" t="n">
-        <v>6924101</v>
+        <v>6924185</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3636,22 +3531,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,48 +3573,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132921994</v>
+        <v>124932515</v>
       </c>
       <c r="B29" t="n">
-        <v>92348</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6040186</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596258</v>
+        <v>596444</v>
       </c>
       <c r="R29" t="n">
-        <v>6924175</v>
+        <v>6924201</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3743,22 +3643,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,7 +3667,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3786,10 +3685,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132921972</v>
+        <v>124926902</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3815,27 +3714,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596129</v>
+        <v>596234</v>
       </c>
       <c r="R30" t="n">
-        <v>6924181</v>
+        <v>6924156</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3859,27 +3755,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3894,22 +3790,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132921974</v>
+        <v>124927157</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,27 +3831,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder bas, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596144</v>
+        <v>596290</v>
       </c>
       <c r="R31" t="n">
-        <v>6924196</v>
+        <v>6924176</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3979,27 +3872,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färskt påbörjat ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4014,22 +3907,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132921975</v>
+        <v>124927193</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,27 +3948,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596162</v>
+        <v>596249</v>
       </c>
       <c r="R32" t="n">
-        <v>6924167</v>
+        <v>6924197</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4099,27 +3989,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall. Sitter högt upp</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4134,22 +4024,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132921978</v>
+        <v>124931177</v>
       </c>
       <c r="B33" t="n">
-        <v>83183</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4157,37 +4047,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596210</v>
+        <v>596344</v>
       </c>
       <c r="R33" t="n">
-        <v>6924094</v>
+        <v>6924086</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4211,22 +4106,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Ser även ut attt finnas något färskt hack.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4253,10 +4153,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132921965</v>
+        <v>124931444</v>
       </c>
       <c r="B34" t="n">
-        <v>91928</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4264,37 +4164,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Hömyran, Hömyran, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596255</v>
+        <v>596351</v>
       </c>
       <c r="R34" t="n">
-        <v>6924162</v>
+        <v>6924073</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4318,22 +4223,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4348,22 +4258,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132921981</v>
+        <v>124931615</v>
       </c>
       <c r="B35" t="n">
-        <v>83183</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4371,37 +4281,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596306</v>
+        <v>596369</v>
       </c>
       <c r="R35" t="n">
-        <v>6924187</v>
+        <v>6924080</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4425,22 +4340,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4467,10 +4387,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132921963</v>
+        <v>124932344</v>
       </c>
       <c r="B36" t="n">
-        <v>57958</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,27 +4416,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Himmelsmyran, Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596161</v>
+        <v>596451</v>
       </c>
       <c r="R36" t="n">
-        <v>6924185</v>
+        <v>6924184</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4540,27 +4457,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall. Kan vara årsfärska</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4575,22 +4492,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132921966</v>
+        <v>132921963</v>
       </c>
       <c r="B37" t="n">
-        <v>83183</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4598,37 +4515,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596320</v>
+        <v>596161</v>
       </c>
       <c r="R37" t="n">
-        <v>6924149</v>
+        <v>6924185</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4657,7 +4582,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4667,7 +4592,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall. Kan vara årsfärska</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4694,10 +4624,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132921968</v>
+        <v>132921971</v>
       </c>
       <c r="B38" t="n">
-        <v>83183</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4705,34 +4635,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596333</v>
+        <v>596126</v>
       </c>
       <c r="R38" t="n">
-        <v>6924148</v>
+        <v>6924182</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4759,27 +4697,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4806,10 +4744,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132921982</v>
+        <v>132921972</v>
       </c>
       <c r="B39" t="n">
-        <v>80439</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4817,34 +4755,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596355</v>
+        <v>596129</v>
       </c>
       <c r="R39" t="n">
-        <v>6924159</v>
+        <v>6924181</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4876,7 +4822,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4886,7 +4832,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4913,10 +4864,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132921969</v>
+        <v>132921973</v>
       </c>
       <c r="B40" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4924,34 +4875,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596029</v>
+        <v>596134</v>
       </c>
       <c r="R40" t="n">
-        <v>6924204</v>
+        <v>6924194</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4983,7 +4942,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4993,7 +4952,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5020,10 +4984,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132921970</v>
+        <v>132921974</v>
       </c>
       <c r="B41" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5031,34 +4995,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596081</v>
+        <v>596144</v>
       </c>
       <c r="R41" t="n">
-        <v>6924192</v>
+        <v>6924196</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5090,7 +5062,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5100,7 +5072,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5127,10 +5104,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132921971</v>
+        <v>132921975</v>
       </c>
       <c r="B42" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5170,10 +5147,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596126</v>
+        <v>596162</v>
       </c>
       <c r="R42" t="n">
-        <v>6924182</v>
+        <v>6924167</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5205,7 +5182,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5215,12 +5192,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på tall. Sitter högt upp</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5247,10 +5224,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132921995</v>
+        <v>132921977</v>
       </c>
       <c r="B43" t="n">
-        <v>83183</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5258,34 +5235,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596284</v>
+        <v>596162</v>
       </c>
       <c r="R43" t="n">
-        <v>6924197</v>
+        <v>6924158</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5312,22 +5297,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5354,56 +5344,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132921973</v>
+        <v>105899098</v>
       </c>
       <c r="B44" t="n">
-        <v>57958</v>
+        <v>57141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjärdalsberget, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596134</v>
+        <v>596349</v>
       </c>
       <c r="R44" t="n">
-        <v>6924194</v>
+        <v>6924180</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5427,27 +5409,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5462,68 +5429,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Dennis Jonason</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Dennis Jonason</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132921977</v>
+        <v>124328603</v>
       </c>
       <c r="B45" t="n">
-        <v>57958</v>
+        <v>57141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäder spillning , Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>596162</v>
+        <v>596290</v>
       </c>
       <c r="R45" t="n">
-        <v>6924158</v>
+        <v>6924176</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5547,27 +5511,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5582,60 +5541,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132921967</v>
+        <v>124422816</v>
       </c>
       <c r="B46" t="n">
-        <v>91942</v>
+        <v>57141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Tjäderbajs, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>596336</v>
+        <v>596139</v>
       </c>
       <c r="R46" t="n">
-        <v>6924145</v>
+        <v>6924224</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5659,22 +5618,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:32</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:32</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5698,6 +5647,1655 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124423161</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tjäderbajs, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>596087</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6924169</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124423338</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Tjäderbajs, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>596099</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6924148</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Dropping</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>124664148</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tjäder, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>596235</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6924189</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>124924660</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>596399</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6924236</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>124927331</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>596228</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6924195</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>124928083</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>596173</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6924184</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>124928235</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>596183</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6924165</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>124930808</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>596344</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6924086</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132921993</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>596056</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6924180</v>
+      </c>
+      <c r="S55" t="n">
+        <v>8</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre spillning nedanför tall. Möjligt natträd</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>124931729</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hömyran, Hömyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>596350</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6924076</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>105899203</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Tjärdalsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>596361</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6924211</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>124927907</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>596183</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6924165</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>124925426</v>
+      </c>
+      <c r="B59" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>596395</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6924217</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>124929330</v>
+      </c>
+      <c r="B60" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>596232</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6924082</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132921994</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92366</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>596258</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6924175</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18532-2025 artfynd.xlsx
+++ b/artfynd/A 18532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921969</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921970</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921979</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124326926</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921965</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921967</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921966</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921968</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921978</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921981</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,6 +1899,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921995</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1951,6 +2011,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921996</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2058,6 +2123,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124931273</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2165,6 +2235,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921984</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2272,6 +2347,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921985</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2379,6 +2459,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921997</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2486,6 +2571,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921998</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2593,6 +2683,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921999</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2703,6 +2798,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118719202</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2810,6 +2910,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124929444</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2917,6 +3022,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124929949</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3024,6 +3134,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921980</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3131,6 +3246,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921982</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3241,6 +3361,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118719201</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3356,6 +3481,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124329435</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3458,6 +3588,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124422845</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3570,6 +3705,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124926296</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3682,6 +3822,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124932515</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3799,6 +3944,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124926902</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3916,6 +4066,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124927157</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4033,6 +4188,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124927193</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4150,6 +4310,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124931177</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4267,6 +4432,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124931444</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4384,6 +4554,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124931615</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4501,6 +4676,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124932344</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4621,6 +4801,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921963</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4741,6 +4926,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921971</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4861,6 +5051,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921972</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4981,6 +5176,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921973</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5101,6 +5301,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921974</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5221,6 +5426,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921975</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5341,6 +5551,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921977</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5438,6 +5653,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899098</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5550,6 +5770,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124328603</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5647,6 +5872,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124422816</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5754,6 +5984,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124423161</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5861,6 +6096,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124423338</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5970,6 +6210,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124664148</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6082,6 +6327,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124924660</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6194,6 +6444,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124927331</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6306,6 +6561,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124928083</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6418,6 +6678,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124928235</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6530,6 +6795,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124930808</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6650,6 +6920,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921993</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6766,6 +7041,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124931729</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6863,6 +7143,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899203</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6974,6 +7259,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124927907</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7081,6 +7371,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124925426</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7188,6 +7483,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124929330</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7296,8 +7596,75 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132921994</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>